--- a/public/researcharea.xlsx
+++ b/public/researcharea.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ryandias/Sites/intranet/storage/app/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE740F4B-7C67-5641-8522-8367C61FC80E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55D16D19-24DA-4641-90F2-F6E3818A7DC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11580" yWindow="5400" windowWidth="28040" windowHeight="17440" xr2:uid="{F39D1B68-7E7B-4C4A-B926-876CFC1E7FA8}"/>
+    <workbookView xWindow="24000" yWindow="3260" windowWidth="28040" windowHeight="17440" xr2:uid="{F39D1B68-7E7B-4C4A-B926-876CFC1E7FA8}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,24 +35,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>Cyber Security</t>
-  </si>
-  <si>
-    <t>Data Science</t>
-  </si>
-  <si>
-    <t>Digital Games</t>
-  </si>
-  <si>
-    <t>Digital Innovation</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Business Process Management and Enterprise Modeling</t>
   </si>
   <si>
     <t>Name</t>
+  </si>
+  <si>
+    <t>AI and data science</t>
+  </si>
+  <si>
+    <t>Cybersecurity</t>
+  </si>
+  <si>
+    <t>Digital Games and simulation</t>
+  </si>
+  <si>
+    <t>Digital transformation and governace</t>
+  </si>
+  <si>
+    <t>Human-computer interaction</t>
+  </si>
+  <si>
+    <t>Risk and decision analysis</t>
+  </si>
+  <si>
+    <t>Language technology</t>
+  </si>
+  <si>
+    <t>Technology enhanced learning</t>
   </si>
 </sst>
 </file>
@@ -404,7 +416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CC55D72C-88A9-D94C-A4A0-73376C18547D}">
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="54" customWidth="1"/>
@@ -412,32 +424,52 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
-        <v>3</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
